--- a/오지훈.xlsx
+++ b/오지훈.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F01A5B65-16CC-4D36-8A42-E1C867A8C066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8276CA2C-802B-405E-935C-3CDA39E280AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
   <si>
     <t>교시</t>
   </si>
@@ -79,13 +79,17 @@
   </si>
   <si>
     <t>근면</t>
+  </si>
+  <si>
+    <t>동아리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +110,13 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -183,7 +194,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -196,6 +207,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -205,10 +222,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -549,11 +563,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
       <c r="D2" s="2">
         <v>303</v>
       </c>
@@ -565,9 +579,9 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
       <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
@@ -579,92 +593,92 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="7"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="2">
         <v>101</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
       <c r="F4" s="2">
         <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="2">
         <v>104</v>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="2">
         <v>102</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
-      <c r="B7" s="4"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="2">
         <v>303</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="2">
         <v>301</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="5"/>
       <c r="F8" s="2">
         <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
+      <c r="A9" s="8"/>
       <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="6"/>
       <c r="D9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="6"/>
       <c r="F9" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="7"/>
+      <c r="B10" s="5"/>
       <c r="C10" s="2">
         <v>103</v>
       </c>
@@ -674,11 +688,13 @@
       <c r="E10" s="2">
         <v>302</v>
       </c>
-      <c r="F10" s="7"/>
+      <c r="F10" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
-      <c r="B11" s="4"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
@@ -688,35 +704,37 @@
       <c r="E11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2">
         <v>208</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
+      <c r="A13" s="8"/>
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="7"/>
+      <c r="B14" s="5"/>
       <c r="C14" s="2">
         <v>301</v>
       </c>
@@ -726,11 +744,11 @@
       <c r="E14" s="2">
         <v>301</v>
       </c>
-      <c r="F14" s="7"/>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="3" t="s">
         <v>17</v>
       </c>
@@ -740,20 +758,37 @@
       <c r="E15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="4"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="B6:B7"/>
@@ -761,24 +796,7 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
